--- a/risques_final.xlsx
+++ b/risques_final.xlsx
@@ -101,7 +101,7 @@
     <t>1-Sinistres physiques (PHY)</t>
   </si>
   <si>
-    <t>test 12</t>
+    <t>test kkkk</t>
   </si>
   <si>
     <t>A, D, E</t>

--- a/risques_final.xlsx
+++ b/risques_final.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="118">
   <si>
     <t>Programme gestion des risques</t>
   </si>
@@ -355,6 +355,45 @@
   </si>
   <si>
     <t>A_SURVEILLER</t>
+  </si>
+  <si>
+    <t>AUTO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vol données </t>
+  </si>
+  <si>
+    <t>Cybercriminel</t>
+  </si>
+  <si>
+    <t>SGBD</t>
+  </si>
+  <si>
+    <t>RSK-4836</t>
+  </si>
+  <si>
+    <t>RH</t>
+  </si>
+  <si>
+    <t>La source [Cybercriminel] exploite la faiblesse [Test] causant [Vol données ] sur l'actif SGBD</t>
+  </si>
+  <si>
+    <t>fffff</t>
+  </si>
+  <si>
+    <t>ACCEPTE</t>
+  </si>
+  <si>
+    <t>Employé malveillant</t>
+  </si>
+  <si>
+    <t>RSK-5804</t>
+  </si>
+  <si>
+    <t>La source [Employé malveillant] exploite la faiblesse [ffff] causant [fffff] sur l'actif SGBD</t>
+  </si>
+  <si>
+    <t>ffff</t>
   </si>
 </sst>
 </file>
@@ -399,7 +438,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:Y18"/>
+  <dimension ref="A1:Y21"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1425,6 +1464,165 @@
       </c>
       <c r="Y18" t="s" s="0">
         <v>104</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="0">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="s" s="0">
+        <v>106</v>
+      </c>
+      <c r="B20" t="s" s="0">
+        <v>107</v>
+      </c>
+      <c r="C20" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D20" t="s" s="0">
+        <v>109</v>
+      </c>
+      <c r="E20" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="F20" t="s" s="0">
+        <v>111</v>
+      </c>
+      <c r="G20" t="s" s="0">
+        <v>100</v>
+      </c>
+      <c r="H20" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="I20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="K20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="N20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O20" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="P20" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="Q20" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="R20" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="S20" t="s" s="0">
+        <v>102</v>
+      </c>
+      <c r="T20" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="U20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="W20" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X20" t="n" s="0">
+        <v>7.0</v>
+      </c>
+      <c r="Y20" t="s" s="0">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="s" s="0">
+        <v>112</v>
+      </c>
+      <c r="B21" t="s" s="0">
+        <v>114</v>
+      </c>
+      <c r="C21" t="s" s="0">
+        <v>108</v>
+      </c>
+      <c r="D21" t="s" s="0">
+        <v>115</v>
+      </c>
+      <c r="E21" t="s" s="0">
+        <v>110</v>
+      </c>
+      <c r="F21" t="s" s="0">
+        <v>116</v>
+      </c>
+      <c r="G21" t="s" s="0">
+        <v>117</v>
+      </c>
+      <c r="H21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="I21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="K21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M21" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="N21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="O21" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="P21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="Q21" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="R21" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="S21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="T21" t="s" s="0">
+        <v>101</v>
+      </c>
+      <c r="U21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="V21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="W21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="X21" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="Y21" t="s" s="0">
+        <v>101</v>
       </c>
     </row>
   </sheetData>
